--- a/output/full_scan/batch_seq6_2026-06-22.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-22.xlsx
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6415</v>
+        <v>6257</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1222.513716588245</v>
+        <v>1235.76954120663</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>673</v>
+        <v>242.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.98787001935186</v>
+        <v>64.20404645683077</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.86728742720888</v>
+        <v>27.52445723015365</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.354616567675678</v>
+        <v>2.182837363914051</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>1</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4.266115137202064</v>
+        <v>0.7893270278889402</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6257</v>
+        <v>6415</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1215.76954120663</v>
+        <v>1222.513716588245</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>242.5</v>
+        <v>673</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.20404645683077</v>
+        <v>66.98787001935186</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.52445723015365</v>
+        <v>27.86728742720888</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.182837363914051</v>
+        <v>2.354616567675678</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>1</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7893270278889402</v>
+        <v>4.266115137202064</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6435</v>
+        <v>6271</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1165.207620282458</v>
+        <v>1172.986592783368</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>349</v>
+        <v>266.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.10282340950839</v>
+        <v>64.24358277257826</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29.06303213575171</v>
+        <v>26.43904771026768</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2174668720718798</v>
+        <v>3.046049548946924</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.341564650546722</v>
+        <v>-0.4858912132232031</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6271</v>
+        <v>6435</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1157.986592783368</v>
+        <v>1165.207620282458</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>266.5</v>
+        <v>349</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,29 +923,29 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.24358277257826</v>
+        <v>74.10282340950839</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.43904771026768</v>
+        <v>29.06303213575171</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.046049548946924</v>
+        <v>0.2174668720718798</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.4858912132232031</v>
+        <v>3.341564650546722</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1130.605430569954</v>
+        <v>1150.605430569954</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>31.1</v>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1007.519697804113</v>
+        <v>997.5196978041128</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>97.2</v>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>939.7208796610248</v>
+        <v>949.7208796610248</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>38.35</v>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6451</v>
+        <v>6282</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>761.0019185940325</v>
+        <v>766.5641204986298</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>617</v>
+        <v>63.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.33568182600086</v>
+        <v>58.55972708898098</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.11931170361538</v>
+        <v>31.38753500682633</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.15896498985467</v>
+        <v>0.8819779510114427</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-8.482328342727115</v>
+        <v>-0.5085945680500159</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6282</v>
+        <v>6451</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>756.5641204986298</v>
+        <v>761.0019185940325</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>63.9</v>
+        <v>617</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.55972708898098</v>
+        <v>57.33568182600086</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>31.38753500682633</v>
+        <v>32.11931170361538</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8819779510114427</v>
+        <v>1.15896498985467</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.5085945680500159</v>
+        <v>-8.482328342727115</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>618.3487641781219</v>
+        <v>608.3487641781219</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>83.09999999999999</v>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>584.3449736615671</v>
+        <v>594.3449736615671</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>134.5</v>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>344.0623419507396</v>
+        <v>329.0623419507396</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>39</v>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6246</v>
+        <v>6226</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>321.2926025667705</v>
+        <v>324.5270205765061</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15.35</v>
+        <v>12.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.36685134335679</v>
+        <v>47.95352750956579</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.56104647028084</v>
+        <v>13.42941845221206</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9886562203149321</v>
+        <v>0.6672309565296523</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>2</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0039927306546469</v>
+        <v>-0.0870051656056928</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6230</v>
+        <v>6246</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>319.1948903728893</v>
+        <v>321.2926025667705</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>135</v>
+        <v>15.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.72777273350233</v>
+        <v>46.36685134335679</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.50673783869418</v>
+        <v>17.56104647028084</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5832158385899915</v>
+        <v>0.9886562203149321</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2940331175268151</v>
+        <v>-0.0039927306546469</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>314.5270205765061</v>
+        <v>319.1948903728893</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>12.5</v>
+        <v>135</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.95352750956579</v>
+        <v>45.72777273350233</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.42941845221206</v>
+        <v>12.50673783869418</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6672309565296523</v>
+        <v>0.5832158385899915</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,11 +5287,11 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0870051656056928</v>
+        <v>0.2940331175268151</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6216</v>
+        <v>6176</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>228.1434890348388</v>
+        <v>228.8480948863965</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>23.3</v>
+        <v>90.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>53.2253218148581</v>
+        <v>38.61297861512627</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.02621570282329</v>
+        <v>28.60535134726064</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5575212104461752</v>
+        <v>1.281212761903083</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.09594091132618909</v>
+        <v>-1.001463651668665</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6176</v>
+        <v>6216</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>218.8480948863965</v>
+        <v>228.1434890348388</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>90.2</v>
+        <v>23.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>38.61297861512627</v>
+        <v>53.2253218148581</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>28.60535134726064</v>
+        <v>18.02621570282329</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.281212761903083</v>
+        <v>0.5575212104461752</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,11 +5976,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.001463651668665</v>
+        <v>0.09594091132618909</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq6_2026-06-22.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-22.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.74006384705962</v>
+        <v>68.74006384323437</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.6265834561342</v>
+        <v>31.626583373829</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.066677819577645</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.20404645683077</v>
+        <v>64.20404644948016</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.52445723015365</v>
+        <v>27.52445711277542</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.182837363914051</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.7893270278889402</v>
+        <v>0.7893270281980076</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.98787001935186</v>
+        <v>66.98787000001468</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.86728742720888</v>
+        <v>27.8672874763523</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.354616567675678</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4.266115137202064</v>
+        <v>4.26611513709905</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.65974354992446</v>
+        <v>65.6597435419086</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.80293134026183</v>
+        <v>14.80293132311954</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.184170737576002</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.156680465031867</v>
+        <v>3.156680465134887</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.74035165891325</v>
+        <v>63.74035165528494</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.57009255980181</v>
+        <v>25.5700924772138</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.117177694718507</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.187706306848791</v>
+        <v>1.187706307065151</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.61242061007538</v>
+        <v>71.61242058991033</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>31.4183099364307</v>
+        <v>31.4183099785135</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.785509349928146</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7169972240314721</v>
+        <v>0.716997224113896</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.24358277257826</v>
+        <v>64.24358275656337</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.43904771026768</v>
+        <v>26.43904760422274</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3.046049548946924</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4858912132232031</v>
+        <v>-0.4858912130171546</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>74.10282340950839</v>
+        <v>74.10282339317592</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.06303213575171</v>
+        <v>29.06303213584101</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.2174668720718798</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.341564650546722</v>
+        <v>3.341564650876403</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.39792122208765</v>
+        <v>65.39792117664368</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.62029526148829</v>
+        <v>19.62029518841324</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.82277810798152</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.412919973531676</v>
+        <v>0.4129199736140978</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.56055270964458</v>
+        <v>66.27963871117393</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.40171085346697</v>
+        <v>25.15350990936851</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.476371134358034</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1963166730240125</v>
+        <v>0.1976960959148643</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>78.41355755854876</v>
+        <v>78.41355753805335</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>49.3493522627881</v>
+        <v>49.34935223340926</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2.221367767441132</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.9872666509222908</v>
+        <v>0.9872666510150154</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>72.40046560566367</v>
+        <v>72.40046561500105</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>54.63628739451757</v>
+        <v>54.63628740404225</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>3.030051062385514</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5368429219123108</v>
+        <v>0.5368429218917032</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.28955634243646</v>
+        <v>66.28955633295753</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>40.08069450227247</v>
+        <v>40.08069439510973</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.8519697804112841</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.9431711597905466</v>
+        <v>0.9431711598935656</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>70.79929817020033</v>
+        <v>70.7992981131934</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.92135164163842</v>
+        <v>21.92135177426542</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.05836980168995</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.623490376010301</v>
+        <v>1.623490376525444</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>72.8154773245476</v>
+        <v>72.81547730548159</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>62.38028790745878</v>
+        <v>62.38028797594762</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.180611686208258</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.9693956331253144</v>
+        <v>0.9693956335580456</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.33242311896285</v>
+        <v>71.33242310674444</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41.65741569196251</v>
+        <v>41.65741565435238</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2.133260415523628</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2.007555338848398</v>
+        <v>2.007555338941119</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.46751760216336</v>
+        <v>57.46751751704617</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14.39059194208423</v>
+        <v>14.39059216656685</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>2.116662428236752</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0626283914377036</v>
+        <v>0.0626283919322433</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.22168013188669</v>
+        <v>63.22168011785905</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.25782422591389</v>
+        <v>33.25782424483049</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.669817944176484</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>68.58558265519031</v>
+        <v>68.58558264767248</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.17315733495653</v>
+        <v>24.17315733627106</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>4.741088877591391</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5013637565646243</v>
+        <v>0.5013637568015925</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>70.69103894685306</v>
+        <v>70.69103890435701</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46.50725325218625</v>
+        <v>46.50725334479562</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.615036341074278</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3202305866758608</v>
+        <v>0.3202305867273756</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.1647416719571</v>
+        <v>60.16474154827149</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.55713102586107</v>
+        <v>15.55713103012932</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.839184090404006</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0279087650443171</v>
+        <v>0.0279087650649228</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.84300244128178</v>
+        <v>62.84300231095372</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.05399920027215</v>
+        <v>24.05399947163188</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.9297960507710376</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>7.583705821467412</v>
+        <v>7.583705826824955</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>76.55398512904597</v>
+        <v>76.55398508818226</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>41.62172446941548</v>
+        <v>41.62172443911255</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8133621225806428</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>6.882658540412926</v>
+        <v>6.882658544740153</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>71.27401600062173</v>
+        <v>71.2740159797264</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.50141759641214</v>
+        <v>29.50141753901048</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.390948334045853</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.633208959355288</v>
+        <v>1.633208959396494</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6197</v>
+        <v>6442</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>838.3309788843384</v>
+        <v>854.6086269244964</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>353</v>
+        <v>2085</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>71.96808826338292</v>
+        <v>55.6095372788189</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45.50043375698754</v>
+        <v>10.9739388937754</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7051915136343661</v>
+        <v>0.5699927272064429</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.5769943411757552</v>
+        <v>5.648677386846336</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6414</v>
+        <v>6197</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>833.3119468987527</v>
+        <v>838.3309788843384</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.87351240962492</v>
+        <v>71.968088216586</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.91161119100798</v>
+        <v>45.50043362941999</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5930279652707443</v>
+        <v>0.7051915136343661</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-2.530510749752661</v>
+        <v>-0.5769943399394499</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6189</v>
+        <v>6414</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>825.3805747419103</v>
+        <v>833.3119468987527</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>54.6</v>
+        <v>381</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.25616230041063</v>
+        <v>55.87351238699482</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.89520234095922</v>
+        <v>27.91161119464732</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5312907509311237</v>
+        <v>0.5930279652707443</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0014423947798396</v>
+        <v>-2.530510749340545</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6419</v>
+        <v>6189</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>824.2339842462364</v>
+        <v>825.3805747419104</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>152.5</v>
+        <v>54.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.9656079583953</v>
+        <v>56.25616225051941</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.22709472592821</v>
+        <v>28.89520237893695</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.713754440895167</v>
+        <v>0.5312907509311237</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5620882795184052</v>
+        <v>-0.0014423946562045</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6292</v>
+        <v>6419</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>824.0515677725705</v>
+        <v>824.2339842462364</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>68</v>
+        <v>152.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>65.34906185566869</v>
+        <v>55.96560790734436</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>35.81020489026363</v>
+        <v>15.22709501751568</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8826679688765104</v>
+        <v>1.713754440895167</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.3327985215441162</v>
+        <v>0.5620882811050861</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6204</v>
+        <v>6292</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>819.3647786524646</v>
+        <v>824.0515677725705</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>115.5</v>
+        <v>68</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>65.2675301672551</v>
+        <v>65.34906182520498</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>42.69895525171701</v>
+        <v>35.81020489817298</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.131915402941108</v>
+        <v>0.8826679688765104</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1272613696475986</v>
+        <v>0.3327985217501794</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6207</v>
+        <v>6204</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>816.5338956186703</v>
+        <v>819.3647786524646</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>165.5</v>
+        <v>115.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>73.42437887220061</v>
+        <v>65.26753014677888</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>66.48949348319468</v>
+        <v>42.69895521565753</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.260656579735612</v>
+        <v>1.131915402941108</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.054835965308605</v>
+        <v>-0.1272613688645796</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6409</v>
+        <v>6207</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>812.3631062466056</v>
+        <v>816.5338956186703</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>943</v>
+        <v>165.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.25609520196178</v>
+        <v>73.42437885566127</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37.7286641957004</v>
+        <v>66.48949335676073</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4102639723768825</v>
+        <v>1.260656579735612</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>10.91837752302527</v>
+        <v>2.054835965679509</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6175</v>
+        <v>6409</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>806.2327926315015</v>
+        <v>812.3631062466058</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>109</v>
+        <v>943</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.14356129478742</v>
+        <v>65.25609522913629</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>41.20587592427595</v>
+        <v>37.72866419103802</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7552172931838054</v>
+        <v>0.4102639723768825</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0348301145661782</v>
+        <v>10.91837752714645</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6465</v>
+        <v>6175</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>795.5530167069613</v>
+        <v>806.2327926315015</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>70.5</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>70.17439122835907</v>
+        <v>61.14356128428238</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.16216704387597</v>
+        <v>41.20587589784343</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.172392199604817</v>
+        <v>0.7552172931838054</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.813431697742052</v>
+        <v>0.0348301146692247</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6265</v>
+        <v>6465</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>790.9457204990294</v>
+        <v>795.5530167069614</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>59.8</v>
+        <v>70.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.61298252522607</v>
+        <v>70.17439120852237</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>34.19404726284868</v>
+        <v>30.16216694535514</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.88327838742112</v>
+        <v>1.172392199604817</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>1</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.3626090255089806</v>
+        <v>1.81343169813052</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6432</v>
+        <v>6265</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>787.8422086357981</v>
+        <v>790.9457204990294</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>81.3</v>
+        <v>59.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>65.61800866817771</v>
+        <v>60.61298252123093</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46.01920449453073</v>
+        <v>34.19404720226684</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.319106534951146</v>
+        <v>0.88327838742112</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.7303027233218176</v>
+        <v>-0.3626090254924921</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6191</v>
+        <v>6432</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>767.001808941118</v>
+        <v>787.8422086357981</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>103.5</v>
+        <v>81.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.47918787069434</v>
+        <v>65.61800866099534</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.45330613112079</v>
+        <v>46.01920447099682</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.487352537788275</v>
+        <v>1.319106534951146</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.7966393056192962</v>
+        <v>0.7303027233939421</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6282</v>
+        <v>6191</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>766.5641204986298</v>
+        <v>767.0018089411176</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>63.9</v>
+        <v>103.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.55972708898098</v>
+        <v>58.47918783391226</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.38753500682633</v>
+        <v>16.4533060971336</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8819779510114427</v>
+        <v>1.487352537788275</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5085945680500159</v>
+        <v>0.7966393057841419</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6451</v>
+        <v>6282</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>761.0019185940325</v>
+        <v>766.5641204986298</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>617</v>
+        <v>63.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.33568182600086</v>
+        <v>58.55972706924803</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32.11931170361538</v>
+        <v>31.38753497838979</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.15896498985467</v>
+        <v>0.8819779510114427</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-8.482328342727115</v>
+        <v>-0.5085945679469883</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6223</v>
+        <v>6451</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>750.1799099712662</v>
+        <v>761.0019185940325</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>6425</v>
+        <v>617</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>60.99416353947189</v>
+        <v>57.33568181434664</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.59551495854102</v>
+        <v>32.11931174419631</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4091803612208461</v>
+        <v>1.15896498985467</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>2</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>15.39912074575972</v>
+        <v>-8.482328342108975</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6462</v>
+        <v>6223</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>733.842709049997</v>
+        <v>750.1799099712665</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>122</v>
+        <v>6425</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.63371845909991</v>
+        <v>60.99416352938521</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.71900382571207</v>
+        <v>22.59551488605907</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.936543018446516</v>
+        <v>0.4091803612208461</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0331216329816212</v>
+        <v>15.39912074864546</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6196</v>
+        <v>6462</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>722.8544478652092</v>
+        <v>733.842709049997</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>562</v>
+        <v>122</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>66.52226784730169</v>
+        <v>52.63371836984437</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>41.39169106416361</v>
+        <v>20.71900383969026</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5586756675536658</v>
+        <v>0.936543018446516</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.906421057591217</v>
+        <v>0.0331216334555728</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6275</v>
+        <v>6196</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>715.6791449067609</v>
+        <v>722.8544478652092</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>51.4</v>
+        <v>562</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>59.49068213749506</v>
+        <v>66.52226784730169</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19.33079400383963</v>
+        <v>41.39169106416361</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.925293135501074</v>
+        <v>0.5586756675536658</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1070035608409967</v>
+        <v>0.9064210574881812</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6291</v>
+        <v>6275</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>698.4693083072503</v>
+        <v>715.6791449067611</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>591</v>
+        <v>51.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.95562539545488</v>
+        <v>59.49068202093394</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.22442780805473</v>
+        <v>19.33079390179688</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9652116640539642</v>
+        <v>2.925293135501074</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-7.026333836889002</v>
+        <v>0.1070035611912996</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6470</v>
+        <v>6291</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>684.2579553551851</v>
+        <v>698.4693083072503</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>50.5</v>
+        <v>591</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>62.68550206132203</v>
+        <v>56.9556253881361</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.93084987518392</v>
+        <v>22.22442784583276</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.268578437834956</v>
+        <v>0.9652116640539642</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0822442778507938</v>
+        <v>-7.026333836806533</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6449</v>
+        <v>6470</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>669.022247187415</v>
+        <v>684.2579553551858</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>428.5</v>
+        <v>50.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>63.76490798513508</v>
+        <v>62.68550192529595</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>43.70521718197808</v>
+        <v>14.93084987806495</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.844007954015052</v>
+        <v>1.268578437834956</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.6735185838347775</v>
+        <v>0.0822442779229238</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6218</v>
+        <v>6449</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>650.4071747379053</v>
+        <v>669.022247187415</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>37.1</v>
+        <v>428.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.08532925328441</v>
+        <v>63.76490797285436</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.49362653181519</v>
+        <v>43.70521708712429</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.477627157904712</v>
+        <v>2.844007954015052</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.002547849726217</v>
+        <v>-0.6735185831135766</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6174</v>
+        <v>6218</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>634.3700429674185</v>
+        <v>650.4071747379053</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>51</v>
+        <v>37.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>59.8963631429378</v>
+        <v>53.08532923083722</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>37.78942224917509</v>
+        <v>12.49362658351245</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.44972891463329</v>
+        <v>1.477627157904712</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0178895156270355</v>
+        <v>0.0025478497159098</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6233</v>
+        <v>6174</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>626.9582735516763</v>
+        <v>634.3700429674185</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>26.1</v>
+        <v>51</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56.32527649413095</v>
+        <v>59.89636313632576</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.59875323094995</v>
+        <v>37.78942226905264</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.096756012665795</v>
+        <v>0.44972891463329</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1840787465043036</v>
+        <v>-0.0178895155858263</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6224</v>
+        <v>6233</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>608.3487641781219</v>
+        <v>626.9582735516763</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.38929830538232</v>
+        <v>56.32527644164284</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.98186292041941</v>
+        <v>14.59875308809812</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.004568046450519</v>
+        <v>2.096756012665795</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.6685306495353753</v>
+        <v>0.1840787465661221</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6206</v>
+        <v>6224</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>594.3449736615671</v>
+        <v>608.3487641781219</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>134.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.25565287612747</v>
+        <v>54.38929828529289</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.12899684621382</v>
+        <v>25.98186292509332</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5935453412045152</v>
+        <v>1.004568046450519</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.518695301353701</v>
+        <v>-0.6685306494117351</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6283</v>
+        <v>6206</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>582.3769093189558</v>
+        <v>594.3449736615671</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>24.15</v>
+        <v>134.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.08130289325821</v>
+        <v>54.25565283002648</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.99364363320674</v>
+        <v>21.1289968331708</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4857541739044868</v>
+        <v>0.5935453412045152</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1219585167578343</v>
+        <v>-1.518695301250656</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>571.0789186723069</v>
+        <v>582.3769093189558</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>122</v>
+        <v>24.15</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>57.18346527181352</v>
+        <v>50.08130282428828</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.97763835937262</v>
+        <v>16.99364376651354</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9417771488775196</v>
+        <v>0.4857541739044868</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2588451432184038</v>
+        <v>-0.1219585166445052</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6190</v>
+        <v>6279</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>566.0775237060005</v>
+        <v>571.0789186723068</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>83.7</v>
+        <v>122</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.57216805983103</v>
+        <v>57.18346490096767</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.88756906523849</v>
+        <v>19.97763896178216</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.149351629808785</v>
+        <v>0.9417771488775196</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.4519450046794289</v>
+        <v>-0.2588451417759949</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6474</v>
+        <v>6190</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>565.9075010646806</v>
+        <v>566.0775237060005</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>83.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.75862689575124</v>
+        <v>57.57216802840716</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.80282144148127</v>
+        <v>26.88756900892734</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.549351941543127</v>
+        <v>1.149351629808785</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1706035627180055</v>
+        <v>-0.4519450045145736</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6217</v>
+        <v>6474</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>563.8125075098916</v>
+        <v>565.9075010646806</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>271.5</v>
+        <v>38</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.70556601325881</v>
+        <v>51.75862689214574</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.13048845863666</v>
+        <v>18.80282147960061</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.058667962735083</v>
+        <v>1.549351941543127</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.8316987066628867</v>
+        <v>0.1706035627180055</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6277</v>
+        <v>6217</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>563.3799333723741</v>
+        <v>563.8125075098916</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>71.5</v>
+        <v>271.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.61435094938032</v>
+        <v>53.70556601345778</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32.51220344641263</v>
+        <v>14.1304884694043</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6450534100362871</v>
+        <v>2.058667962735083</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.7906418173752989</v>
+        <v>-0.831698706683512</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6405</v>
+        <v>6277</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>563.1364711285237</v>
+        <v>563.3799333723741</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>68.5</v>
+        <v>71.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.26292586104316</v>
+        <v>40.6143509060333</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>33.68352128664527</v>
+        <v>32.51220341102602</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.045117505494177</v>
+        <v>0.6450534100362871</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.720821777912741</v>
+        <v>-0.7906418173134946</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6278</v>
+        <v>6405</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>558.0768038788617</v>
+        <v>563.1364711285237</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>206</v>
+        <v>68.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.40735288746267</v>
+        <v>52.26292583814666</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.96831280594364</v>
+        <v>33.68352128705951</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3964261828402045</v>
+        <v>2.045117505494177</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.50140352902633</v>
+        <v>-1.720821777655166</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6177</v>
+        <v>6278</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>553.4984810625717</v>
+        <v>558.0768038788617</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>45.9</v>
+        <v>206</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.00460591321043</v>
+        <v>51.40735287995977</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.22994070178283</v>
+        <v>22.96831282292498</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.468978572944754</v>
+        <v>0.3964261828402045</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.386156391652818</v>
+        <v>-2.501403528511188</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6245</v>
+        <v>6177</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>552.4586458849416</v>
+        <v>553.4984810625717</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.54206762263526</v>
+        <v>50.00460586197533</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.47456440685585</v>
+        <v>23.22994076198347</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5281088592289421</v>
+        <v>2.468978572944754</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.8718778545836363</v>
+        <v>0.3861563917661497</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6170</v>
+        <v>6245</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>534.8080107220998</v>
+        <v>552.4586458849416</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>52.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>59.04937308501183</v>
+        <v>45.54206752685308</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.17418065164079</v>
+        <v>18.47456445922324</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6561150005724489</v>
+        <v>0.5281088592289421</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0331617781591389</v>
+        <v>-0.8718778543363699</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6263</v>
+        <v>6170</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>529.5655708064405</v>
+        <v>534.8080107220998</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>163</v>
+        <v>52.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.80442614416768</v>
+        <v>59.04937285613448</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.83658871690399</v>
+        <v>16.17418084046849</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5846334413881394</v>
+        <v>0.6561150005724489</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.649199278778085</v>
+        <v>0.0331617784270141</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6485</v>
+        <v>6263</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>524.1719383415009</v>
+        <v>529.5655708064405</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>163</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.10645398046567</v>
+        <v>48.80442613135784</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.00035080360224</v>
+        <v>16.83658872223883</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3904875748002627</v>
+        <v>0.5846334413881394</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.342917642597258</v>
+        <v>-1.649199278572027</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6284</v>
+        <v>6485</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>514.7097506543249</v>
+        <v>524.171938341501</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>103.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>52.32798449561957</v>
+        <v>45.10645396934993</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>42.79894994350146</v>
+        <v>20.00035075790882</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6534058452701512</v>
+        <v>0.3904875748002627</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>1</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.9724124437759012</v>
+        <v>-2.342917642453008</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6438</v>
+        <v>6284</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>513.5663189814035</v>
+        <v>514.7097506543249</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>159.5</v>
+        <v>103.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.77751969132657</v>
+        <v>52.32798446925718</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.01752091262653</v>
+        <v>42.79894989938728</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7859556826673563</v>
+        <v>0.6534058452701512</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5906556971099697</v>
+        <v>-0.9724124435080208</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6164</v>
+        <v>6438</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>512.1821719794167</v>
+        <v>513.5663189814035</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>13.7</v>
+        <v>159.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>60.48973974467792</v>
+        <v>49.77751958189857</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.40113749930231</v>
+        <v>25.01752088312432</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.496466698209992</v>
+        <v>0.7859556826673563</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0895736763430815</v>
+        <v>0.5906556977281516</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6214</v>
+        <v>6164</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>509.671594792609</v>
+        <v>512.1821719794167</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>141</v>
+        <v>13.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>55.28044751331148</v>
+        <v>60.48973972648226</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.97942156288625</v>
+        <v>19.4011374553752</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.679746185918605</v>
+        <v>1.496466698209992</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.025360009623504</v>
+        <v>0.08957367637399059</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6227</v>
+        <v>6214</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>507.7810195349956</v>
+        <v>509.671594792609</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.96897369249202</v>
+        <v>55.28044729937057</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.97302103946372</v>
+        <v>19.97942179458622</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4492624588578395</v>
+        <v>1.679746185918605</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.952605384410231</v>
+        <v>-1.02536000879928</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6244</v>
+        <v>6227</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>491.9214581977525</v>
+        <v>507.7810195349956</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>28.6</v>
+        <v>125</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.92191652233024</v>
+        <v>52.968973631011</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.54706303372947</v>
+        <v>23.97302093985769</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2740116000346663</v>
+        <v>0.4492624588578395</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1917249148037532</v>
+        <v>-1.952605384410231</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6285</v>
+        <v>6244</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>491.7230978579947</v>
+        <v>491.9214581977524</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>268</v>
+        <v>28.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.38449821582321</v>
+        <v>46.92191649236603</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.93771296441951</v>
+        <v>20.5470631007588</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7747801955978744</v>
+        <v>0.2740116000346663</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-4.801118763601043</v>
+        <v>-0.1917249148243637</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6426</v>
+        <v>6285</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>474.6417959240181</v>
+        <v>491.7230978579947</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.58730850777914</v>
+        <v>46.38449818817335</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.65610368234844</v>
+        <v>21.93771311962535</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5953574894210645</v>
+        <v>0.7747801955978744</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-3.445107052398789</v>
+        <v>-4.80111876298287</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6417</v>
+        <v>6426</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>430.5367504885507</v>
+        <v>474.6417959240181</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>132.5</v>
+        <v>217</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.41843014961552</v>
+        <v>46.58730850236665</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.91526475173444</v>
+        <v>20.65610368234843</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5134680134680135</v>
+        <v>0.5953574894210645</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.484295282939792</v>
+        <v>-3.445107052501791</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6205</v>
+        <v>6417</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>429.6118928369095</v>
+        <v>430.5367504885507</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>132.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.28988019445217</v>
+        <v>49.41843013604988</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.0973497577556</v>
+        <v>17.91526469748618</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4805807972602386</v>
+        <v>0.5134680134680135</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2164356215039857</v>
+        <v>-1.484295282836782</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6464</v>
+        <v>6205</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>428.5382211553432</v>
+        <v>429.6118928369095</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>78</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>60.85130967207191</v>
+        <v>53.2898801351796</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.19213215433418</v>
+        <v>14.09734980841596</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1649232901870161</v>
+        <v>0.4805807972602386</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0605431606126655</v>
+        <v>-0.2164356210300377</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6234</v>
+        <v>6464</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>426.0806619427161</v>
+        <v>428.5382211553432</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46.8</v>
+        <v>78</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.25767171230445</v>
+        <v>60.85130971854257</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.65205570821447</v>
+        <v>14.19213227744756</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6360693598172907</v>
+        <v>0.1649232901870161</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>1</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2870650244501302</v>
+        <v>-0.0605431606126655</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6237</v>
+        <v>6234</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>415.8601000301594</v>
+        <v>426.0806619427161</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>47.65</v>
+        <v>46.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.29439915339904</v>
+        <v>51.25767169098955</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.36280407444476</v>
+        <v>17.65205564190063</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.680830137957192</v>
+        <v>0.6360693598172907</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.5485067614181913</v>
+        <v>-0.2870650243058947</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6418</v>
+        <v>6237</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>396.4369782776536</v>
+        <v>415.8601000301594</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>32.1</v>
+        <v>47.65</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.05886090292231</v>
+        <v>52.29439907809546</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.37466989572776</v>
+        <v>23.36280396982314</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5452295306088797</v>
+        <v>0.680830137957192</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0262576097906506</v>
+        <v>-0.5485067611297102</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6222</v>
+        <v>6418</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>394.8592450832517</v>
+        <v>396.4369782776536</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>20.55</v>
+        <v>32.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.82501665571143</v>
+        <v>52.05886086671861</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25.48612597173344</v>
+        <v>25.37466985991912</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.821850506519737</v>
+        <v>0.5452295306088797</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0288942944811719</v>
+        <v>0.0262576098421647</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6225</v>
+        <v>6222</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>391.9478146237103</v>
+        <v>394.8592450832517</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>21.6</v>
+        <v>20.55</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>38.65309836943576</v>
+        <v>46.8250108028978</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.0977182152271</v>
+        <v>25.48612245738282</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9134569785388482</v>
+        <v>1.821850506519737</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2569874001332046</v>
+        <v>0.0288942990968718</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6412</v>
+        <v>6225</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>390.9767640380484</v>
+        <v>391.9478146237103</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>95</v>
+        <v>21.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.07267840724506</v>
+        <v>38.65309838517454</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.52977056848037</v>
+        <v>13.09771850941637</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.066716121322847</v>
+        <v>0.9134569785388482</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.90858359320376</v>
+        <v>-0.256987400298052</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6290</v>
+        <v>6412</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>390.8087172482921</v>
+        <v>390.9767640380484</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>318</v>
+        <v>95</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>54.13394336161614</v>
+        <v>52.07267837572388</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.63661109222391</v>
+        <v>21.52977064085776</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.893020564489533</v>
+        <v>1.066716121322847</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-4.183873161847066</v>
+        <v>-0.9085835929976984</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6266</v>
+        <v>6290</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>378.1136311685572</v>
+        <v>390.8087172482921</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>26.05</v>
+        <v>318</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.04627651516961</v>
+        <v>54.13394334728641</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.75012305577586</v>
+        <v>16.63661101995738</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6521992654689309</v>
+        <v>0.893020564489533</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1641761768013678</v>
+        <v>-4.183873161373152</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6228</v>
+        <v>6266</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>376.8969509323507</v>
+        <v>378.1136311685572</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>20.1</v>
+        <v>26.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.90469852225366</v>
+        <v>40.04627644953587</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3.801068296297756</v>
+        <v>22.75012307358033</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.753788351831136</v>
+        <v>0.6521992654689309</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.072652561370478</v>
+        <v>-0.1641761767807603</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6198</v>
+        <v>6228</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>370.2750567543945</v>
+        <v>376.8969509323797</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.13539186438294</v>
+        <v>45.90469832538306</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>8.362131074356355</v>
+        <v>3.801068408251377</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6140122374080312</v>
+        <v>1.753788351831136</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.4609421927930713</v>
+        <v>-0.0726525611232085</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6261</v>
+        <v>6198</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>366.3074164893355</v>
+        <v>370.2750567543944</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>101</v>
+        <v>20.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.77464381420728</v>
+        <v>51.13539186344173</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.13808082602105</v>
+        <v>8.362131084461202</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5649100867226665</v>
+        <v>0.6140122374080312</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.222284471486681</v>
+        <v>0.4609421927209543</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6443</v>
+        <v>6261</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>329.0623419507396</v>
+        <v>366.3074164893355</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.30371379931753</v>
+        <v>46.7746437917954</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.28559817091741</v>
+        <v>23.13808083241761</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.37930169944568</v>
+        <v>0.5649100867226665</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1835603307676327</v>
+        <v>-1.222284471321834</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6226</v>
+        <v>6443</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>324.5270205765061</v>
+        <v>329.0623419507396</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>12.5</v>
+        <v>39</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.95352750956579</v>
+        <v>46.30371377300418</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.42941845221206</v>
+        <v>18.28559830729732</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6672309565296523</v>
+        <v>0.37930169944568</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0870051656056928</v>
+        <v>-0.1835603307367158</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6246</v>
+        <v>6226</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>321.2926025667705</v>
+        <v>324.5270205765061</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>15.35</v>
+        <v>12.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.36685134335679</v>
+        <v>47.95352750469176</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.56104647028084</v>
+        <v>13.42941840951071</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9886562203149321</v>
+        <v>0.6672309565296523</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>2</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0039927306546469</v>
+        <v>-0.0870051655995118</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6230</v>
+        <v>6246</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>319.1948903728893</v>
+        <v>321.29260256677</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>135</v>
+        <v>15.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.72777273350233</v>
+        <v>46.36685130907305</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.50673783869418</v>
+        <v>17.56104644911283</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5832158385899915</v>
+        <v>0.9886562203149321</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2940331175268151</v>
+        <v>-0.0039927306134364</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6423</v>
+        <v>6230</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>307.3359448283995</v>
+        <v>319.1948903728893</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>84.2</v>
+        <v>135</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.43498636785137</v>
+        <v>45.7277726454975</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>26.80866232698617</v>
+        <v>12.50673777959525</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4186488656811546</v>
+        <v>0.5832158385899915</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.153697049261746</v>
+        <v>0.2940331176298327</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6416</v>
+        <v>6423</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>285.5697049404827</v>
+        <v>307.3359448283995</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>83.2</v>
+        <v>84.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.32483906330086</v>
+        <v>39.43498633318144</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.22728723789293</v>
+        <v>26.80866231394716</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6960255329322026</v>
+        <v>0.4186488656811546</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5646113163605873</v>
+        <v>-0.153697049261746</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6194</v>
+        <v>6416</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>284.2530516984303</v>
+        <v>285.5697049404827</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>32.2</v>
+        <v>83.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.80429359770481</v>
+        <v>43.32483893496769</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.87383212216483</v>
+        <v>23.22728722892255</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.932888993068182</v>
+        <v>0.6960255329322026</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1605076777371916</v>
+        <v>-0.5646113161751328</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6167</v>
+        <v>6194</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>272.3579268477453</v>
+        <v>284.2530516984303</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>12.05</v>
+        <v>32.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.22425210835869</v>
+        <v>40.80429345104477</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.86273676521218</v>
+        <v>17.87383219120219</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7915687792656132</v>
+        <v>0.932888993068182</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0628444254971709</v>
+        <v>-0.1605076775929489</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6192</v>
+        <v>6167</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>265.0507737399</v>
+        <v>272.3579268477452</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>119</v>
+        <v>12.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.03366543074948</v>
+        <v>51.22425212711812</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25.6883695827028</v>
+        <v>12.86273687240667</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7885145502934313</v>
+        <v>0.7915687792656132</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.232477849435194</v>
+        <v>0.0628444254088838</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6456</v>
+        <v>6192</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>260.3171313150661</v>
+        <v>265.0507737399</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>119</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.32391952630265</v>
+        <v>42.03366541583132</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.82905690316719</v>
+        <v>25.68836956301936</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3798304501628966</v>
+        <v>0.7885145502934313</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.5675578115642426</v>
+        <v>-1.232477849126106</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6210</v>
+        <v>6456</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>258.2854567038172</v>
+        <v>260.3171313150661</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.95</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.27346830375142</v>
+        <v>51.32391951675115</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.4029529212981</v>
+        <v>12.82905691770654</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3726261711383984</v>
+        <v>0.3798304501628966</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.06982021587978229</v>
+        <v>-0.5675578115127309</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6272</v>
+        <v>6210</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>251.302743122862</v>
+        <v>258.2854567038172</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>32.15</v>
+        <v>20.95</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.07865420541666</v>
+        <v>51.2734683431509</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26.81518634816195</v>
+        <v>18.40295301354141</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4989246110392846</v>
+        <v>0.3726261711383984</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.6668880523349402</v>
+        <v>-0.0698202159312962</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6215</v>
+        <v>6272</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>251.0205879443045</v>
+        <v>251.302743122862</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>109.5</v>
+        <v>32.15</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.53135420331496</v>
+        <v>40.07865364496183</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.51876844195592</v>
+        <v>26.81518663377648</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.347303054454963</v>
+        <v>0.4989246110392846</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.320245790088696</v>
+        <v>-0.6668880511810142</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6276</v>
+        <v>6215</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>250.7613980025056</v>
+        <v>251.0205879443046</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>24.1</v>
+        <v>109.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>32.06538336527676</v>
+        <v>43.53135421989784</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.26037721222933</v>
+        <v>19.51876836863648</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.231600033771667</v>
+        <v>0.347303054454963</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0676534437203464</v>
+        <v>-1.320245788460846</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6184</v>
+        <v>6276</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>243.0343170590054</v>
+        <v>250.7613980025071</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46.8</v>
+        <v>24.1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.98154463965998</v>
+        <v>32.06538284210974</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>29.71900164788958</v>
+        <v>21.26037753522385</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.321888967771127</v>
+        <v>2.231600033771667</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0880953778076016</v>
+        <v>-0.0676534429579316</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6176</v>
+        <v>6184</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>228.8480948863965</v>
+        <v>243.0343170590054</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>90.2</v>
+        <v>46.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.61297861512627</v>
+        <v>53.98154466833292</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>28.60535134726064</v>
+        <v>29.71900169386724</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.281212761903083</v>
+        <v>1.321888967771127</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.001463651668665</v>
+        <v>0.0880953778282083</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6216</v>
+        <v>6176</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>228.1434890348388</v>
+        <v>228.8480948863965</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>23.3</v>
+        <v>90.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.2253218148581</v>
+        <v>38.61297851358409</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.02621570282329</v>
+        <v>28.605351316625</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5575212104461752</v>
+        <v>1.281212761903083</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.09594091132618909</v>
+        <v>-1.001463651256552</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6165</v>
+        <v>6216</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>212.1371004890852</v>
+        <v>228.1434890348387</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>48</v>
+        <v>23.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.3489202385318</v>
+        <v>53.22532166636685</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.861067335761</v>
+        <v>18.02621582238002</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.074584813040255</v>
+        <v>0.5575212104461752</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0589961395413277</v>
+        <v>0.0959409115013365</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6203</v>
+        <v>6165</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>209.841184649876</v>
+        <v>212.1371004890852</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>48</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.36275518668931</v>
+        <v>45.348920169526</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.41532971670081</v>
+        <v>18.86106735945934</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6512241604469819</v>
+        <v>1.074584813040255</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.3759704361065769</v>
+        <v>-0.058996139088002</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6201</v>
+        <v>6203</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>202.5740110346628</v>
+        <v>209.841184649876</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>48.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.52071658226534</v>
+        <v>46.36275510781024</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>18.00688551901764</v>
+        <v>22.4153297286348</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.501835094181555</v>
+        <v>0.6512241604469819</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,48 +6135,48 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1284699406408343</v>
+        <v>-0.3759704359211283</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6287</v>
+        <v>6201</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>201.7982208587868</v>
+        <v>202.5740110346628</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>48.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G108" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.71399387501272</v>
+        <v>49.5207166245163</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0.96425253178819</v>
+        <v>18.00688557303054</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>1.501835094181555</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,48 +6188,48 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0153085825903483</v>
+        <v>0.1284699407026575</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6281</v>
+        <v>6287</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>199.0533278991124</v>
+        <v>201.6336657121454</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>51.4</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G109" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.03333073458173</v>
+        <v>51.71399387501272</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.51587466870689</v>
+        <v>0.9322078587835469</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9590921881387696</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.07836004640552</v>
+        <v>-0.0153085825903483</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6441</v>
+        <v>6281</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>192.9296616334786</v>
+        <v>199.0533278991124</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>22.85</v>
+        <v>51.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.98475296983469</v>
+        <v>50.03333075201542</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.2429505145154</v>
+        <v>12.51587473726792</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4100841523016188</v>
+        <v>0.9590921881387696</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1385761699061469</v>
+        <v>0.0783600463849225</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6188</v>
+        <v>6441</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>188.4676367045892</v>
+        <v>192.9296616334786</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>79.3</v>
+        <v>22.85</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.94362008377024</v>
+        <v>44.98475298566833</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.85691719323996</v>
+        <v>11.24295053794475</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6908727207374323</v>
+        <v>0.4100841523016188</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3022090377502695</v>
+        <v>-0.1385761694219097</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6235</v>
+        <v>6188</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>172.7103019014025</v>
+        <v>188.46763670459</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>41.3</v>
+        <v>79.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.85577933254714</v>
+        <v>41.94361992118336</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.17809694524126</v>
+        <v>12.85691720648291</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4570299071999185</v>
+        <v>0.6908727207374323</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1401323395235798</v>
+        <v>-0.3022090370908843</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6477</v>
+        <v>6235</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>167.674767304736</v>
+        <v>172.7103019014025</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.4</v>
+        <v>41.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.65567071197326</v>
+        <v>45.85577932632783</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.72544040058904</v>
+        <v>16.17809690197284</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5352287300086838</v>
+        <v>0.4570299071999185</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>2</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1031274279635924</v>
+        <v>-0.1401323394720663</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6183</v>
+        <v>6477</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>159.6668772929801</v>
+        <v>167.6747673047352</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>90</v>
+        <v>32.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.0420327077258</v>
+        <v>44.65567062800272</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.55784815153553</v>
+        <v>12.72544040955234</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.040500286423525</v>
+        <v>0.5352287300086838</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,62 +6506,115 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1144407766077009</v>
+        <v>-0.1031274279120849</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>6183</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>關貿</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>159.6668772929801</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>45.04203257040452</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>16.55784813479224</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.040500286423525</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.1144407767313441</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
         <v>6236</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>中湛</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>130.273785641869</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>48.02625788120114</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>7.824988437643279</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.4113394600970746</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>130.2737856418693</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>48.02625868147452</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>7.824987976672691</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.4113394658460937</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, obv_uptrend</t>
         </is>
